--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
+        <v>90958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>91932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31068-2024 artfynd.xlsx
+++ b/artfynd/A 31068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743033</v>
       </c>
       <c r="B2" t="n">
-        <v>91932</v>
+        <v>91933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
